--- a/jogos_2025-03-19.xlsx
+++ b/jogos_2025-03-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -125,60 +125,6 @@
   </si>
   <si>
     <t>awayGoals</t>
-  </si>
-  <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
   </si>
   <si>
     <t>DateTime</t>
@@ -644,10 +590,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD7"/>
+  <dimension ref="A1:AL7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,79 +708,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45735</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -849,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L2">
         <v>1.9</v>
@@ -924,87 +816,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="AK2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL2">
-        <v>1.2</v>
-      </c>
-      <c r="AM2">
-        <v>1.3</v>
-      </c>
-      <c r="AN2">
-        <v>1.73</v>
-      </c>
-      <c r="AO2">
-        <v>10</v>
-      </c>
-      <c r="AP2">
-        <v>1.31</v>
-      </c>
-      <c r="AQ2">
-        <v>1.58</v>
-      </c>
-      <c r="AR2">
-        <v>2.01</v>
-      </c>
-      <c r="AS2">
-        <v>2.62</v>
-      </c>
-      <c r="AT2">
-        <v>3.68</v>
-      </c>
-      <c r="AU2">
-        <v>2.92</v>
-      </c>
-      <c r="AV2">
-        <v>2.12</v>
-      </c>
-      <c r="AW2">
-        <v>1.68</v>
-      </c>
-      <c r="AX2">
-        <v>1.38</v>
-      </c>
-      <c r="AY2">
-        <v>1.2</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.57</v>
-      </c>
-      <c r="BC2">
-        <v>2.88</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>66</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45735.625</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45735</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1019,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L3">
         <v>2.12</v>
@@ -1094,87 +932,33 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="AK3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>9</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.57</v>
-      </c>
-      <c r="BC3">
-        <v>3.2</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>63</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45735.6875</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45735</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1189,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L4">
         <v>2.5</v>
@@ -1264,87 +1048,33 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="AK4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>12</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.67</v>
-      </c>
-      <c r="BC4">
-        <v>2.75</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>67</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45735.70833333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45735</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1359,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L5">
         <v>3.4</v>
@@ -1434,87 +1164,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ5" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="AK5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL5">
-        <v>1.67</v>
-      </c>
-      <c r="AM5">
-        <v>1.31</v>
-      </c>
-      <c r="AN5">
-        <v>1.18</v>
-      </c>
-      <c r="AO5">
-        <v>9</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>2</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>1.8</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>2.75</v>
-      </c>
-      <c r="BC5">
-        <v>1.62</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>68</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45735.72916666666</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45735</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1529,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L6">
         <v>3.1</v>
@@ -1604,87 +1280,33 @@
         <v>1.09</v>
       </c>
       <c r="AJ6" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="AK6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL6">
-        <v>1.62</v>
-      </c>
-      <c r="AM6">
-        <v>1.25</v>
-      </c>
-      <c r="AN6">
-        <v>1.3</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2.3</v>
-      </c>
-      <c r="BC6">
-        <v>1.8</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>69</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45735.77083333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45735</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1699,7 +1321,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L7">
         <v>1.8</v>
@@ -1774,66 +1396,12 @@
         <v>1.07</v>
       </c>
       <c r="AJ7" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL7">
-        <v>1.28</v>
-      </c>
-      <c r="AM7">
-        <v>1.33</v>
-      </c>
-      <c r="AN7">
-        <v>1.68</v>
-      </c>
-      <c r="AO7">
-        <v>6</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.73</v>
-      </c>
-      <c r="BC7">
-        <v>2.38</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>70</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45735.83333333334</v>
       </c>
     </row>
